--- a/inputs/Jumps Racing Program.xlsx
+++ b/inputs/Jumps Racing Program.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://racingvictorialtd057-my.sharepoint.com/personal/s_cunliffe_racingvictoria_net_au/Documents/AAA Strategy &amp; Projects/Inside Racing/August/Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1687D078-137B-418B-A167-959F42BC1108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/inputs/Jumps Racing Program.xlsx
+++ b/inputs/Jumps Racing Program.xlsx
@@ -8,6 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://racingvictorialtd057-my.sharepoint.com/personal/s_cunliffe_racingvictoria_net_au/Documents/AAA Strategy &amp; Projects/Inside Racing/August/Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1687D078-137B-418B-A167-959F42BC1108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
